--- a/artfynd/A 28305-2026 artfynd.xlsx
+++ b/artfynd/A 28305-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390067</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390078</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390042</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390043</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,6 +1289,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390044</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1390,6 +1420,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390047</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1516,6 +1551,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390052</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1623,6 +1663,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390054</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1730,6 +1775,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390058</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1856,6 +1906,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390074</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1982,6 +2037,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390075</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2108,6 +2168,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390077</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2234,6 +2299,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390079</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2360,6 +2430,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390062</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2486,6 +2561,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390064</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2612,6 +2692,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390048</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2719,6 +2804,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390049</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2845,6 +2935,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390060</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2971,6 +3066,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390061</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3097,6 +3197,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390063</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3223,6 +3328,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390065</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3349,6 +3459,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390068</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3475,6 +3590,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390071</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3601,6 +3721,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390072</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3727,6 +3852,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390073</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3853,6 +3983,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390076</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3973,6 +4108,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390045</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4093,6 +4233,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390055</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4213,6 +4358,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390056</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4333,6 +4483,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390057</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4440,6 +4595,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390059</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4547,8 +4707,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134390070</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>